--- a/public/templates/import/opening-balances-v1.xlsx
+++ b/public/templates/import/opening-balances-v1.xlsx
@@ -72,7 +72,7 @@
     <t>—</t>
   </si>
   <si>
-    <t>10.500</t>
+    <t>10</t>
   </si>
   <si>
     <t>Đơn giá vốn đầu kỳ</t>
